--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/88.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/88.xlsx
@@ -426,13 +426,13 @@
         <v>-9.019172314397597</v>
       </c>
       <c r="E2">
-        <v>-8.835575640183352</v>
+        <v>-7.49613001277259</v>
       </c>
       <c r="F2">
-        <v>-6.221954688251889</v>
+        <v>-6.978657541933</v>
       </c>
       <c r="G2">
-        <v>-11.42333317247656</v>
+        <v>-10.34427078558774</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.266221760998532</v>
       </c>
       <c r="E3">
-        <v>-9.621274937462173</v>
+        <v>-8.920529812567247</v>
       </c>
       <c r="F3">
-        <v>-6.455010058457709</v>
+        <v>-6.952419832816728</v>
       </c>
       <c r="G3">
-        <v>-10.680311021097</v>
+        <v>-10.62343915927786</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.610071030219206</v>
       </c>
       <c r="E4">
-        <v>-9.995969933804835</v>
+        <v>-8.017380013425486</v>
       </c>
       <c r="F4">
-        <v>-6.832203427669152</v>
+        <v>-6.895483656120111</v>
       </c>
       <c r="G4">
-        <v>-10.86488386654798</v>
+        <v>-10.70422971261823</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.998984771408542</v>
       </c>
       <c r="E5">
-        <v>-12.20044466616079</v>
+        <v>-9.673669381730919</v>
       </c>
       <c r="F5">
-        <v>-6.150573440785252</v>
+        <v>-6.942249137845156</v>
       </c>
       <c r="G5">
-        <v>-10.75557627393233</v>
+        <v>-10.29839986659559</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.41239200223575</v>
       </c>
       <c r="E6">
-        <v>-11.75359749345392</v>
+        <v>-10.53481758445154</v>
       </c>
       <c r="F6">
-        <v>-6.362373731802641</v>
+        <v>-6.608354118594343</v>
       </c>
       <c r="G6">
-        <v>-10.96385924653557</v>
+        <v>-10.15331189779149</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.82514504523395</v>
       </c>
       <c r="E7">
-        <v>-13.82031151802253</v>
+        <v>-11.07596117142013</v>
       </c>
       <c r="F7">
-        <v>-6.009125564920223</v>
+        <v>-6.39210839390983</v>
       </c>
       <c r="G7">
-        <v>-10.0556011461999</v>
+        <v>-10.22872612517609</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.20214269983322</v>
       </c>
       <c r="E8">
-        <v>-12.69237279761402</v>
+        <v>-11.80445225656005</v>
       </c>
       <c r="F8">
-        <v>-5.685199118994698</v>
+        <v>-6.470599932978397</v>
       </c>
       <c r="G8">
-        <v>-10.39699453384617</v>
+        <v>-10.10854339046393</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.51873792308953</v>
       </c>
       <c r="E9">
-        <v>-14.0664250233914</v>
+        <v>-12.51962057116941</v>
       </c>
       <c r="F9">
-        <v>-6.160715971265129</v>
+        <v>-6.419449074222929</v>
       </c>
       <c r="G9">
-        <v>-11.189860258865</v>
+        <v>-9.483767304656054</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.7518494951264</v>
       </c>
       <c r="E10">
-        <v>-16.11697239575263</v>
+        <v>-12.67829830039818</v>
       </c>
       <c r="F10">
-        <v>-5.877548515026952</v>
+        <v>-6.267463950810589</v>
       </c>
       <c r="G10">
-        <v>-10.09937648986569</v>
+        <v>-9.344681354914654</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.87753394252344</v>
       </c>
       <c r="E11">
-        <v>-15.5169495897363</v>
+        <v>-14.39641492433033</v>
       </c>
       <c r="F11">
-        <v>-5.627867811046944</v>
+        <v>-6.26112901109768</v>
       </c>
       <c r="G11">
-        <v>-9.782931373403372</v>
+        <v>-9.317137616027917</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.89569426390994</v>
       </c>
       <c r="E12">
-        <v>-15.69094261805902</v>
+        <v>-14.44846067610049</v>
       </c>
       <c r="F12">
-        <v>-5.502512628716101</v>
+        <v>-6.145963576188673</v>
       </c>
       <c r="G12">
-        <v>-9.642921781456515</v>
+        <v>-8.626574369263643</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.79986901049558</v>
       </c>
       <c r="E13">
-        <v>-16.06044345471488</v>
+        <v>-15.19787783962986</v>
       </c>
       <c r="F13">
-        <v>-5.461505128807914</v>
+        <v>-6.005469151204266</v>
       </c>
       <c r="G13">
-        <v>-10.14936903805422</v>
+        <v>-8.826965001301268</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.60573446826093</v>
       </c>
       <c r="E14">
-        <v>-17.14315177673478</v>
+        <v>-16.65660347240266</v>
       </c>
       <c r="F14">
-        <v>-4.788936238759537</v>
+        <v>-5.379869521262023</v>
       </c>
       <c r="G14">
-        <v>-9.394644108193333</v>
+        <v>-8.103408857692617</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.33634507724755</v>
       </c>
       <c r="E15">
-        <v>-18.60901881301767</v>
+        <v>-16.82955948017761</v>
       </c>
       <c r="F15">
-        <v>-5.04128759924617</v>
+        <v>-5.369512443624821</v>
       </c>
       <c r="G15">
-        <v>-9.073779413436093</v>
+        <v>-7.598749295686118</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.01140735585142</v>
       </c>
       <c r="E16">
-        <v>-19.33494225339524</v>
+        <v>-18.46241852396736</v>
       </c>
       <c r="F16">
-        <v>-4.415629983585731</v>
+        <v>-4.924556549945872</v>
       </c>
       <c r="G16">
-        <v>-8.190873470840163</v>
+        <v>-7.511556147272794</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.670666035524</v>
       </c>
       <c r="E17">
-        <v>-19.18275835589347</v>
+        <v>-18.81787203425143</v>
       </c>
       <c r="F17">
-        <v>-4.822426304487318</v>
+        <v>-5.048661725865891</v>
       </c>
       <c r="G17">
-        <v>-8.306341988704402</v>
+        <v>-6.996253181357536</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.34237144791512</v>
       </c>
       <c r="E18">
-        <v>-20.58542600892532</v>
+        <v>-19.91484957786949</v>
       </c>
       <c r="F18">
-        <v>-4.049924827700014</v>
+        <v>-4.469386057823002</v>
       </c>
       <c r="G18">
-        <v>-7.944068990341957</v>
+        <v>-7.302107862639724</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.05659221891449</v>
       </c>
       <c r="E19">
-        <v>-21.35407560156526</v>
+        <v>-20.60929106694574</v>
       </c>
       <c r="F19">
-        <v>-3.966025292042271</v>
+        <v>-4.515547659711408</v>
       </c>
       <c r="G19">
-        <v>-7.659828860885671</v>
+        <v>-6.746472520419526</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.845512073531104</v>
       </c>
       <c r="E20">
-        <v>-22.94785844314282</v>
+        <v>-21.73432250704133</v>
       </c>
       <c r="F20">
-        <v>-3.560735771446377</v>
+        <v>-4.149463939922611</v>
       </c>
       <c r="G20">
-        <v>-6.904729839378845</v>
+        <v>-6.884581859226841</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.715382194273996</v>
       </c>
       <c r="E21">
-        <v>-23.1553033089602</v>
+        <v>-22.47667977959274</v>
       </c>
       <c r="F21">
-        <v>-2.943051192037884</v>
+        <v>-3.762481338928585</v>
       </c>
       <c r="G21">
-        <v>-7.414689584793718</v>
+        <v>-6.586715524330916</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.676713363599966</v>
       </c>
       <c r="E22">
-        <v>-23.72938701586058</v>
+        <v>-23.41961675136589</v>
       </c>
       <c r="F22">
-        <v>-2.967933692083175</v>
+        <v>-3.531030516381987</v>
       </c>
       <c r="G22">
-        <v>-8.660404834129455</v>
+        <v>-6.953603423175106</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.717754760018986</v>
       </c>
       <c r="E23">
-        <v>-24.58494255318173</v>
+        <v>-24.09309593426064</v>
       </c>
       <c r="F23">
-        <v>-3.082743757376381</v>
+        <v>-3.534468241103605</v>
       </c>
       <c r="G23">
-        <v>-7.274256243017835</v>
+        <v>-6.2470204465463</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.813171033545144</v>
       </c>
       <c r="E24">
-        <v>-25.30846137386123</v>
+        <v>-24.27723274436052</v>
       </c>
       <c r="F24">
-        <v>-2.928925042717944</v>
+        <v>-3.079067462842757</v>
       </c>
       <c r="G24">
-        <v>-7.374718057952558</v>
+        <v>-6.866943272593605</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.944430295688509</v>
       </c>
       <c r="E25">
-        <v>-25.11395435828377</v>
+        <v>-23.95473746790428</v>
       </c>
       <c r="F25">
-        <v>-2.74854472728874</v>
+        <v>-3.464409068011836</v>
       </c>
       <c r="G25">
-        <v>-7.488749799052754</v>
+        <v>-7.295274896646667</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.07238791661058</v>
       </c>
       <c r="E26">
-        <v>-25.81642030330161</v>
+        <v>-24.11276762534995</v>
       </c>
       <c r="F26">
-        <v>-2.196235731676587</v>
+        <v>-3.099627541780241</v>
       </c>
       <c r="G26">
-        <v>-7.310702038859671</v>
+        <v>-6.913416710873893</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.17506042968199</v>
       </c>
       <c r="E27">
-        <v>-26.05911481079469</v>
+        <v>-25.0534584740153</v>
       </c>
       <c r="F27">
-        <v>-2.695304725943413</v>
+        <v>-3.117687607896075</v>
       </c>
       <c r="G27">
-        <v>-8.703504826505227</v>
+        <v>-7.269356635619713</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.23054340511952</v>
       </c>
       <c r="E28">
-        <v>-24.83374144363714</v>
+        <v>-25.30029200675139</v>
       </c>
       <c r="F28">
-        <v>-2.444566196790031</v>
+        <v>-3.357675584895926</v>
       </c>
       <c r="G28">
-        <v>-8.481264593908413</v>
+        <v>-7.098542417429938</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.21704296015263</v>
       </c>
       <c r="E29">
-        <v>-25.74886905652919</v>
+        <v>-23.82063576711514</v>
       </c>
       <c r="F29">
-        <v>-2.761001716292039</v>
+        <v>-3.297900593109913</v>
       </c>
       <c r="G29">
-        <v>-8.428050884910167</v>
+        <v>-7.339374673775299</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.13159263890822</v>
       </c>
       <c r="E30">
-        <v>-25.0360419629818</v>
+        <v>-24.0722966531434</v>
       </c>
       <c r="F30">
-        <v>-2.936727435284912</v>
+        <v>-3.29935520626923</v>
       </c>
       <c r="G30">
-        <v>-7.695427157069455</v>
+        <v>-7.722077048660587</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.9637774912352</v>
       </c>
       <c r="E31">
-        <v>-24.35658066592293</v>
+        <v>-24.05478957262975</v>
       </c>
       <c r="F31">
-        <v>-2.738849515206375</v>
+        <v>-3.727010646740711</v>
       </c>
       <c r="G31">
-        <v>-8.268184640818763</v>
+        <v>-7.62585604256167</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.716337666647126</v>
       </c>
       <c r="E32">
-        <v>-24.22187214961676</v>
+        <v>-23.57160139601132</v>
       </c>
       <c r="F32">
-        <v>-2.71218768197987</v>
+        <v>-3.453449767272799</v>
       </c>
       <c r="G32">
-        <v>-7.897118833504012</v>
+        <v>-7.221611947852344</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.399397096837266</v>
       </c>
       <c r="E33">
-        <v>-23.73979344913021</v>
+        <v>-23.16273000633278</v>
       </c>
       <c r="F33">
-        <v>-2.923409772550105</v>
+        <v>-3.510079448030382</v>
       </c>
       <c r="G33">
-        <v>-7.850883754502551</v>
+        <v>-7.194458853339242</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.018710109714281</v>
       </c>
       <c r="E34">
-        <v>-21.77282812152855</v>
+        <v>-22.98982381177191</v>
       </c>
       <c r="F34">
-        <v>-3.051847309986765</v>
+        <v>-3.429099907467508</v>
       </c>
       <c r="G34">
-        <v>-7.850155434483911</v>
+        <v>-6.853883170441179</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.597596376315421</v>
       </c>
       <c r="E35">
-        <v>-23.42530451471952</v>
+        <v>-22.26231993396565</v>
       </c>
       <c r="F35">
-        <v>-3.062937492775445</v>
+        <v>-3.595998543416149</v>
       </c>
       <c r="G35">
-        <v>-8.149561173055597</v>
+        <v>-6.927407076322853</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.154435101477429</v>
       </c>
       <c r="E36">
-        <v>-22.77672288191895</v>
+        <v>-21.86495539674059</v>
       </c>
       <c r="F36">
-        <v>-2.821836189986232</v>
+        <v>-3.445736838385333</v>
       </c>
       <c r="G36">
-        <v>-7.321024319851118</v>
+        <v>-6.964276621993716</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.710298622859292</v>
       </c>
       <c r="E37">
-        <v>-23.5947871829306</v>
+        <v>-21.41134268386626</v>
       </c>
       <c r="F37">
-        <v>-3.125170250645563</v>
+        <v>-3.411092856865452</v>
       </c>
       <c r="G37">
-        <v>-7.248619378361719</v>
+        <v>-5.998616972552625</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.296934754931451</v>
       </c>
       <c r="E38">
-        <v>-21.49680857381303</v>
+        <v>-20.71258555906071</v>
       </c>
       <c r="F38">
-        <v>-2.847141157406951</v>
+        <v>-3.337362359444477</v>
       </c>
       <c r="G38">
-        <v>-6.987251808036258</v>
+        <v>-5.953977576501092</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.929489094066083</v>
       </c>
       <c r="E39">
-        <v>-21.26260495508433</v>
+        <v>-20.76550530631434</v>
       </c>
       <c r="F39">
-        <v>-2.896591377884471</v>
+        <v>-3.642746629425737</v>
       </c>
       <c r="G39">
-        <v>-6.985282033440392</v>
+        <v>-5.746876468655365</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.632780636137124</v>
       </c>
       <c r="E40">
-        <v>-21.86766795267119</v>
+        <v>-20.25269638121174</v>
       </c>
       <c r="F40">
-        <v>-3.359666980132256</v>
+        <v>-3.603998915792387</v>
       </c>
       <c r="G40">
-        <v>-6.495937055098561</v>
+        <v>-5.33568022831357</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.421375942586389</v>
       </c>
       <c r="E41">
-        <v>-21.26077545158523</v>
+        <v>-19.49792656140531</v>
       </c>
       <c r="F41">
-        <v>-3.00169711905388</v>
+        <v>-3.536603772268022</v>
       </c>
       <c r="G41">
-        <v>-6.237231163386674</v>
+        <v>-5.117856263466144</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.298159366283941</v>
       </c>
       <c r="E42">
-        <v>-19.14051675034992</v>
+        <v>-18.80765579689012</v>
       </c>
       <c r="F42">
-        <v>-2.970786589418417</v>
+        <v>-3.479101820635291</v>
       </c>
       <c r="G42">
-        <v>-6.503607589113052</v>
+        <v>-5.140106440035585</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.273266355710355</v>
       </c>
       <c r="E43">
-        <v>-18.82493645370339</v>
+        <v>-19.02340588403756</v>
       </c>
       <c r="F43">
-        <v>-3.36718110084305</v>
+        <v>-3.648338109394633</v>
       </c>
       <c r="G43">
-        <v>-7.012176905401431</v>
+        <v>-5.058445213218383</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.337011121937608</v>
       </c>
       <c r="E44">
-        <v>-19.17275042833652</v>
+        <v>-18.04266521124838</v>
       </c>
       <c r="F44">
-        <v>-2.673594873050844</v>
+        <v>-3.626750854877678</v>
       </c>
       <c r="G44">
-        <v>-6.124007195398061</v>
+        <v>-4.429511082213182</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.481912195288022</v>
       </c>
       <c r="E45">
-        <v>-18.12081308719874</v>
+        <v>-17.70991294116476</v>
       </c>
       <c r="F45">
-        <v>-3.660675813491929</v>
+        <v>-3.530336344498441</v>
       </c>
       <c r="G45">
-        <v>-6.151557555375875</v>
+        <v>-4.774625523045586</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.696636450704148</v>
       </c>
       <c r="E46">
-        <v>-18.48430916732044</v>
+        <v>-16.68529588371526</v>
       </c>
       <c r="F46">
-        <v>-3.349685981295925</v>
+        <v>-3.559069924599347</v>
       </c>
       <c r="G46">
-        <v>-6.881668579152282</v>
+        <v>-4.766753045753199</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.9558148139636</v>
       </c>
       <c r="E47">
-        <v>-16.72984248252871</v>
+        <v>-16.64392374518118</v>
       </c>
       <c r="F47">
-        <v>-3.608947582656711</v>
+        <v>-3.813425105833352</v>
       </c>
       <c r="G47">
-        <v>-6.688276440384677</v>
+        <v>-4.996769749821761</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.246258539279616</v>
       </c>
       <c r="E48">
-        <v>-15.93987283426065</v>
+        <v>-16.06235899922012</v>
       </c>
       <c r="F48">
-        <v>-3.380595682563985</v>
+        <v>-4.046157412752081</v>
       </c>
       <c r="G48">
-        <v>-6.461444481124894</v>
+        <v>-4.361644898658123</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.547527347311007</v>
       </c>
       <c r="E49">
-        <v>-15.99772861818265</v>
+        <v>-15.85164004669521</v>
       </c>
       <c r="F49">
-        <v>-3.501756012367052</v>
+        <v>-4.017997062893913</v>
       </c>
       <c r="G49">
-        <v>-5.251628787617014</v>
+        <v>-5.057207069186695</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.841403176442451</v>
       </c>
       <c r="E50">
-        <v>-15.13739554078341</v>
+        <v>-15.08780875039942</v>
       </c>
       <c r="F50">
-        <v>-3.64462370996048</v>
+        <v>-3.999462342256273</v>
       </c>
       <c r="G50">
-        <v>-5.845441340996087</v>
+        <v>-4.971053432072702</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.126014312059722</v>
       </c>
       <c r="E51">
-        <v>-15.37293505934437</v>
+        <v>-14.77023139671551</v>
       </c>
       <c r="F51">
-        <v>-3.908662506133211</v>
+        <v>-4.243592984637524</v>
       </c>
       <c r="G51">
-        <v>-6.703385770225911</v>
+        <v>-4.475633602666308</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.390477840193485</v>
       </c>
       <c r="E52">
-        <v>-14.43022903974561</v>
+        <v>-13.97142669565849</v>
       </c>
       <c r="F52">
-        <v>-4.053905133070465</v>
+        <v>-4.271787297559208</v>
       </c>
       <c r="G52">
-        <v>-6.727814285760194</v>
+        <v>-4.678457485675297</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.639442719972855</v>
       </c>
       <c r="E53">
-        <v>-14.57872223093113</v>
+        <v>-13.05300688216286</v>
       </c>
       <c r="F53">
-        <v>-3.729573615484972</v>
+        <v>-4.178294439009645</v>
       </c>
       <c r="G53">
-        <v>-6.578084932110036</v>
+        <v>-5.054479179662336</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.878176391575069</v>
       </c>
       <c r="E54">
-        <v>-14.20680318915517</v>
+        <v>-13.46323681404371</v>
       </c>
       <c r="F54">
-        <v>-3.822142016013011</v>
+        <v>-4.476752729136098</v>
       </c>
       <c r="G54">
-        <v>-6.187208820288287</v>
+        <v>-4.885081874963369</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.10600606944173</v>
       </c>
       <c r="E55">
-        <v>-13.74461807498432</v>
+        <v>-12.88594241907189</v>
       </c>
       <c r="F55">
-        <v>-4.086075609525587</v>
+        <v>-4.562810990245536</v>
       </c>
       <c r="G55">
-        <v>-6.995197117330509</v>
+        <v>-5.18382881497274</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.336002303194419</v>
       </c>
       <c r="E56">
-        <v>-13.64629131885577</v>
+        <v>-12.2789140637657</v>
       </c>
       <c r="F56">
-        <v>-3.834568355422407</v>
+        <v>-4.540015147687897</v>
       </c>
       <c r="G56">
-        <v>-6.65015550849997</v>
+        <v>-5.097284533485112</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.565195660735823</v>
       </c>
       <c r="E57">
-        <v>-12.3537742675865</v>
+        <v>-11.51703001129322</v>
       </c>
       <c r="F57">
-        <v>-4.323078150405748</v>
+        <v>-4.638195737369903</v>
       </c>
       <c r="G57">
-        <v>-5.809098172065967</v>
+        <v>-4.594578193346782</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.796507386530802</v>
       </c>
       <c r="E58">
-        <v>-13.33691503159975</v>
+        <v>-11.14286031793544</v>
       </c>
       <c r="F58">
-        <v>-4.134442325440244</v>
+        <v>-4.895977046181886</v>
       </c>
       <c r="G58">
-        <v>-6.631225809106417</v>
+        <v>-4.562088499424376</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.0345403971823</v>
       </c>
       <c r="E59">
-        <v>-11.57058374490792</v>
+        <v>-10.67681241543605</v>
       </c>
       <c r="F59">
-        <v>-4.108471350627674</v>
+        <v>-4.569303733948678</v>
       </c>
       <c r="G59">
-        <v>-6.700916103253615</v>
+        <v>-4.863609676595656</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.27150856290225</v>
       </c>
       <c r="E60">
-        <v>-11.03453016272395</v>
+        <v>-10.71243339198038</v>
       </c>
       <c r="F60">
-        <v>-4.441065833056093</v>
+        <v>-4.836331279710711</v>
       </c>
       <c r="G60">
-        <v>-6.123729109572762</v>
+        <v>-4.577436188544437</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.51537552360806</v>
       </c>
       <c r="E61">
-        <v>-12.21323760523246</v>
+        <v>-10.38574927706705</v>
       </c>
       <c r="F61">
-        <v>-4.651457899488722</v>
+        <v>-4.562970036786874</v>
       </c>
       <c r="G61">
-        <v>-6.731356569487214</v>
+        <v>-4.94299324808184</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.763024009155</v>
       </c>
       <c r="E62">
-        <v>-10.61727656765721</v>
+        <v>-10.64155824528634</v>
       </c>
       <c r="F62">
-        <v>-4.284855621705773</v>
+        <v>-4.982333519556332</v>
       </c>
       <c r="G62">
-        <v>-6.321987750283095</v>
+        <v>-5.075924893665735</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.01008114564972</v>
       </c>
       <c r="E63">
-        <v>-10.41977623076068</v>
+        <v>-10.89855820216964</v>
       </c>
       <c r="F63">
-        <v>-4.492239886098838</v>
+        <v>-4.780517540844885</v>
       </c>
       <c r="G63">
-        <v>-7.183229482870034</v>
+        <v>-5.604956691932349</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.2618411662535</v>
       </c>
       <c r="E64">
-        <v>-11.97138992237881</v>
+        <v>-9.795123054616639</v>
       </c>
       <c r="F64">
-        <v>-4.583881343503144</v>
+        <v>-5.063720616881383</v>
       </c>
       <c r="G64">
-        <v>-7.484879771317346</v>
+        <v>-5.163207426808619</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.50460919678594</v>
       </c>
       <c r="E65">
-        <v>-9.434031594193019</v>
+        <v>-9.574663354501222</v>
       </c>
       <c r="F65">
-        <v>-4.734005539545096</v>
+        <v>-4.744665799651723</v>
       </c>
       <c r="G65">
-        <v>-7.41999638929317</v>
+        <v>-5.410578010594041</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.73787917643328</v>
       </c>
       <c r="E66">
-        <v>-10.82876536076343</v>
+        <v>-9.19860981595626</v>
       </c>
       <c r="F66">
-        <v>-4.735293650856449</v>
+        <v>-4.896914758081855</v>
       </c>
       <c r="G66">
-        <v>-7.366514526106244</v>
+        <v>-5.715571950036018</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.95344844156122</v>
       </c>
       <c r="E67">
-        <v>-10.20086074028188</v>
+        <v>-8.745979781941593</v>
       </c>
       <c r="F67">
-        <v>-4.697783518122882</v>
+        <v>-4.873784255093485</v>
       </c>
       <c r="G67">
-        <v>-6.722798809268197</v>
+        <v>-5.407327054874477</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.13564570201166</v>
       </c>
       <c r="E68">
-        <v>-10.47721086659996</v>
+        <v>-9.195815747493528</v>
       </c>
       <c r="F68">
-        <v>-4.390704408435494</v>
+        <v>-4.932673722125904</v>
       </c>
       <c r="G68">
-        <v>-6.70075719706773</v>
+        <v>-5.234063032985641</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.28437484849526</v>
       </c>
       <c r="E69">
-        <v>-9.524279552691882</v>
+        <v>-8.541627863871462</v>
       </c>
       <c r="F69">
-        <v>-4.901211499800176</v>
+        <v>-4.920157090669604</v>
       </c>
       <c r="G69">
-        <v>-7.482754401081134</v>
+        <v>-5.342688653220208</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.38185497666189</v>
       </c>
       <c r="E70">
-        <v>-10.026768085531</v>
+        <v>-8.436825389911945</v>
       </c>
       <c r="F70">
-        <v>-4.448442444778022</v>
+        <v>-5.045576885657866</v>
       </c>
       <c r="G70">
-        <v>-7.663894210807896</v>
+        <v>-5.700936028206899</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.42622190800001</v>
       </c>
       <c r="E71">
-        <v>-10.26679079335955</v>
+        <v>-9.124293029016382</v>
       </c>
       <c r="F71">
-        <v>-4.995315693493006</v>
+        <v>-5.071669630478647</v>
       </c>
       <c r="G71">
-        <v>-7.090127010669111</v>
+        <v>-5.653413146990662</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.41699243671961</v>
       </c>
       <c r="E72">
-        <v>-11.13254445414597</v>
+        <v>-9.458843103281046</v>
       </c>
       <c r="F72">
-        <v>-4.923325595985312</v>
+        <v>-4.955357735084166</v>
       </c>
       <c r="G72">
-        <v>-6.757016607962105</v>
+        <v>-5.735233279993749</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.34686765095698</v>
       </c>
       <c r="E73">
-        <v>-10.79683961900935</v>
+        <v>-8.952478196691361</v>
       </c>
       <c r="F73">
-        <v>-4.849623263056031</v>
+        <v>-4.994025925446847</v>
       </c>
       <c r="G73">
-        <v>-7.051214858400517</v>
+        <v>-5.282135464761398</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.22662098240425</v>
       </c>
       <c r="E74">
-        <v>-10.68494102627982</v>
+        <v>-9.138145631005846</v>
       </c>
       <c r="F74">
-        <v>-5.065625033540419</v>
+        <v>-5.026019959645172</v>
       </c>
       <c r="G74">
-        <v>-6.278271996437019</v>
+        <v>-5.395667313485164</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.05411886296208</v>
       </c>
       <c r="E75">
-        <v>-10.20625415282501</v>
+        <v>-9.208287164910653</v>
       </c>
       <c r="F75">
-        <v>-4.936718640153774</v>
+        <v>-5.380085725154154</v>
       </c>
       <c r="G75">
-        <v>-6.752785730762916</v>
+        <v>-5.002271876508029</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.83587573836544</v>
       </c>
       <c r="E76">
-        <v>-11.69620814235471</v>
+        <v>-10.71432176564158</v>
       </c>
       <c r="F76">
-        <v>-4.991655137940034</v>
+        <v>-5.359738536639189</v>
       </c>
       <c r="G76">
-        <v>-6.42871311737812</v>
+        <v>-4.476438065232351</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.58724305946837</v>
       </c>
       <c r="E77">
-        <v>-11.18392904871101</v>
+        <v>-10.02580352056737</v>
       </c>
       <c r="F77">
-        <v>-5.294928727778962</v>
+        <v>-5.333795726318314</v>
       </c>
       <c r="G77">
-        <v>-6.713188295567694</v>
+        <v>-4.548127928885269</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.31117990965564</v>
       </c>
       <c r="E78">
-        <v>-12.21307910864219</v>
+        <v>-10.92338329667969</v>
       </c>
       <c r="F78">
-        <v>-5.255150525096529</v>
+        <v>-5.443644699236154</v>
       </c>
       <c r="G78">
-        <v>-6.619705110629753</v>
+        <v>-4.596978338862755</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.02840562691008</v>
       </c>
       <c r="E79">
-        <v>-12.69917003709953</v>
+        <v>-11.35108860975614</v>
       </c>
       <c r="F79">
-        <v>-5.223392575608002</v>
+        <v>-5.593160873604451</v>
       </c>
       <c r="G79">
-        <v>-6.00808844334048</v>
+        <v>-4.313757857432565</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.74926353954709</v>
       </c>
       <c r="E80">
-        <v>-14.49895768976002</v>
+        <v>-11.57976296172147</v>
       </c>
       <c r="F80">
-        <v>-5.241064965779326</v>
+        <v>-5.753858351175736</v>
       </c>
       <c r="G80">
-        <v>-5.349627556670519</v>
+        <v>-4.18614294798474</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.48078543675576</v>
       </c>
       <c r="E81">
-        <v>-13.23948038485071</v>
+        <v>-12.69933759063782</v>
       </c>
       <c r="F81">
-        <v>-5.296550671153643</v>
+        <v>-5.55062834930771</v>
       </c>
       <c r="G81">
-        <v>-5.570470739049761</v>
+        <v>-3.924881315116536</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.24147228490524</v>
       </c>
       <c r="E82">
-        <v>-14.38833612670065</v>
+        <v>-13.29584630082419</v>
       </c>
       <c r="F82">
-        <v>-5.315593181009199</v>
+        <v>-5.685740042908726</v>
       </c>
       <c r="G82">
-        <v>-5.922391661510906</v>
+        <v>-4.266973227871585</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.02901780778472</v>
       </c>
       <c r="E83">
-        <v>-15.77085659887237</v>
+        <v>-14.32048147216972</v>
       </c>
       <c r="F83">
-        <v>-5.681389457309224</v>
+        <v>-6.260099350416</v>
       </c>
       <c r="G83">
-        <v>-6.012666927821292</v>
+        <v>-3.67534894509397</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.855779721021568</v>
       </c>
       <c r="E84">
-        <v>-15.84628286194413</v>
+        <v>-14.13326982821862</v>
       </c>
       <c r="F84">
-        <v>-5.432240565201814</v>
+        <v>-6.117990437363536</v>
       </c>
       <c r="G84">
-        <v>-5.327969967752607</v>
+        <v>-4.413908481086597</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.726171632631839</v>
       </c>
       <c r="E85">
-        <v>-16.70479549279229</v>
+        <v>-15.62090523905638</v>
       </c>
       <c r="F85">
-        <v>-5.85624621889656</v>
+        <v>-6.557889562232096</v>
       </c>
       <c r="G85">
-        <v>-5.234956880281244</v>
+        <v>-4.083423340992233</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.634256865162822</v>
       </c>
       <c r="E86">
-        <v>-18.66254084731433</v>
+        <v>-16.57825634359595</v>
       </c>
       <c r="F86">
-        <v>-6.154830420868239</v>
+        <v>-6.027069659599666</v>
       </c>
       <c r="G86">
-        <v>-5.003165723803633</v>
+        <v>-3.433907548369383</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.587229483951964</v>
       </c>
       <c r="E87">
-        <v>-19.94071622140131</v>
+        <v>-18.26488648775278</v>
       </c>
       <c r="F87">
-        <v>-5.944494683418999</v>
+        <v>-6.258540362963931</v>
       </c>
       <c r="G87">
-        <v>-4.765845956275438</v>
+        <v>-3.365488503709265</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.572787128399698</v>
       </c>
       <c r="E88">
-        <v>-20.70675741301283</v>
+        <v>-19.15891594024309</v>
       </c>
       <c r="F88">
-        <v>-5.956254187069141</v>
+        <v>-6.255111750283744</v>
       </c>
       <c r="G88">
-        <v>-5.18328257495876</v>
+        <v>-3.1386664760861</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.585485374961529</v>
       </c>
       <c r="E89">
-        <v>-21.31037582739124</v>
+        <v>-19.77271889266475</v>
       </c>
       <c r="F89">
-        <v>-6.41610868267114</v>
+        <v>-6.343968236479839</v>
       </c>
       <c r="G89">
-        <v>-5.009273680323588</v>
+        <v>-3.342298132206671</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.621436444838057</v>
       </c>
       <c r="E90">
-        <v>-23.5287258041067</v>
+        <v>-22.21572193642672</v>
       </c>
       <c r="F90">
-        <v>-6.263260400425083</v>
+        <v>-6.466341710344306</v>
       </c>
       <c r="G90">
-        <v>-5.844428314061069</v>
+        <v>-3.869062206778884</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.664027284601524</v>
       </c>
       <c r="E91">
-        <v>-24.56947781444553</v>
+        <v>-24.17146117696337</v>
       </c>
       <c r="F91">
-        <v>-6.016163374374408</v>
+        <v>-6.321673142017191</v>
       </c>
       <c r="G91">
-        <v>-4.715492558623124</v>
+        <v>-4.272402522555989</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.712977380381451</v>
       </c>
       <c r="E92">
-        <v>-27.38640601396886</v>
+        <v>-25.69274314967813</v>
       </c>
       <c r="F92">
-        <v>-6.32014894599604</v>
+        <v>-6.657230280461722</v>
       </c>
       <c r="G92">
-        <v>-6.123073621555986</v>
+        <v>-3.895139373991724</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.758170261624054</v>
       </c>
       <c r="E93">
-        <v>-29.490624860269</v>
+        <v>-27.51939371015212</v>
       </c>
       <c r="F93">
-        <v>-6.220038674449214</v>
+        <v>-6.601629432018417</v>
       </c>
       <c r="G93">
-        <v>-5.927278026726871</v>
+        <v>-4.154593448995485</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.789604387154347</v>
       </c>
       <c r="E94">
-        <v>-31.39099218487686</v>
+        <v>-29.43817607431216</v>
       </c>
       <c r="F94">
-        <v>-6.634837438645545</v>
+        <v>-6.288998603997467</v>
       </c>
       <c r="G94">
-        <v>-5.739262213915042</v>
+        <v>-4.183987782838674</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.810739319447633</v>
       </c>
       <c r="E95">
-        <v>-33.82448090474872</v>
+        <v>-32.20116109145613</v>
       </c>
       <c r="F95">
-        <v>-6.246658675121877</v>
+        <v>-6.302755301455758</v>
       </c>
       <c r="G95">
-        <v>-7.796395485471686</v>
+        <v>-4.930032462295593</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.807420084932685</v>
       </c>
       <c r="E96">
-        <v>-36.19570310701511</v>
+        <v>-34.53238328281277</v>
       </c>
       <c r="F96">
-        <v>-6.253807899991738</v>
+        <v>-6.283280383815941</v>
       </c>
       <c r="G96">
-        <v>-7.005605472505978</v>
+        <v>-5.394021972352146</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.783287144375404</v>
       </c>
       <c r="E97">
-        <v>-37.28768347956571</v>
+        <v>-37.28200024468608</v>
       </c>
       <c r="F97">
-        <v>-6.26807072993314</v>
+        <v>-6.309415375374265</v>
       </c>
       <c r="G97">
-        <v>-7.210799706121085</v>
+        <v>-5.916008929711191</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.733711787220495</v>
       </c>
       <c r="E98">
-        <v>-40.38887531373553</v>
+        <v>-39.37294160519573</v>
       </c>
       <c r="F98">
-        <v>-6.716965924796101</v>
+        <v>-6.290157489993983</v>
       </c>
       <c r="G98">
-        <v>-7.716270351784706</v>
+        <v>-6.2380256943161</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.658539290804143</v>
       </c>
       <c r="E99">
-        <v>-42.81822274412737</v>
+        <v>-41.8976519054781</v>
       </c>
       <c r="F99">
-        <v>-6.727394656213646</v>
+        <v>-6.221603460473101</v>
       </c>
       <c r="G99">
-        <v>-7.28954103177265</v>
+        <v>-7.032775119746776</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.560383762388488</v>
       </c>
       <c r="E100">
-        <v>-43.87663353885911</v>
+        <v>-45.01395072893751</v>
       </c>
       <c r="F100">
-        <v>-6.868658220331553</v>
+        <v>-6.391814323481837</v>
       </c>
       <c r="G100">
-        <v>-8.461229172304744</v>
+        <v>-7.424988691966391</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.448720851694734</v>
       </c>
       <c r="E101">
-        <v>-47.66547415109368</v>
+        <v>-46.61516706059866</v>
       </c>
       <c r="F101">
-        <v>-6.72995265475349</v>
+        <v>-6.378642867593623</v>
       </c>
       <c r="G101">
-        <v>-8.865344155738038</v>
+        <v>-7.547035263817163</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.310364560697856</v>
       </c>
       <c r="E102">
-        <v>-50.29643943337352</v>
+        <v>-48.86197170374131</v>
       </c>
       <c r="F102">
-        <v>-6.713330220265214</v>
+        <v>-6.07990376091762</v>
       </c>
       <c r="G102">
-        <v>-9.51848830627193</v>
+        <v>-8.286776664567309</v>
       </c>
     </row>
   </sheetData>
